--- a/slicer_filter_audit.xlsx
+++ b/slicer_filter_audit.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法人営業部用_売上集計(出荷日基準)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未応答カード一覧'!$A$1:$H$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未応答カード一覧'!$A$1:$H$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'全カード診断結果'!$A$1:$H$823</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +646,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -798,7 +798,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -817,7 +817,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -836,7 +836,7 @@
         <v>22</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -848,7 +848,7 @@
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="10" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>■ 未応答カード一覧（16件）</t>
+          <t>■ 未応答カード一覧（17件）</t>
         </is>
       </c>
     </row>
@@ -1077,36 +1077,36 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>見積予実_元請別</t>
+          <t>【期待値込】プロテック請負金額集計_元請別（計上予定日基準）</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>実績・期待値</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>実績判断</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>平均見積金額_元請別(直近1年間)</t>
+          <t>見積予実_元請別</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>平均日数_施工店別</t>
+          <t>平均見積金額_元請別(直近1年間)</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -1150,7 +1150,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>契約予実_元請別</t>
+          <t>平均日数_施工店別</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>完工予実_元請別</t>
+          <t>契約予実_元請別</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>施工店請負金額_施工店別（工事完了日基準）</t>
+          <t>完工予実_元請別</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>現調数_施工店別（訪問日基準）</t>
+          <t>施工店請負金額_施工店別（工事完了日基準）</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
@@ -1238,7 +1238,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>契約予実_担当別</t>
+          <t>現調数_施工店別（訪問日基準）</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1260,7 +1260,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>対応案件数_施工店別（見積提案日基準）</t>
+          <t>契約予実_担当別</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>契約数_施工店別（結果確定日基準）</t>
+          <t>対応案件数_施工店別（見積提案日基準）</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>見積予実_担当別</t>
+          <t>契約数_施工店別（結果確定日基準）</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>完工予実_元請別（注力外）</t>
+          <t>見積予実_担当別</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1348,7 +1348,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>完工予実_担当別</t>
+          <t>完工予実_元請別（注力外）</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>平均見積金額_元請別(直近3ヶ月)</t>
+          <t>完工予実_担当別</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1392,20 +1392,42 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
+          <t>平均見積金額_元請別(直近3ヶ月)</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>コラボス＋リペイント</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>プロテック請負金額集計_担当別</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>コラボス＋リペイント</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>実績・期待値</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>実績判断</t>
         </is>
@@ -1428,7 +1450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1635,7 +1657,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： APS(出荷基準)</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1679,7 +1701,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 塗料系統(出荷基準)の複製</t>
+          <t>分類名（リファイン_屋根壁分割）</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1723,7 +1745,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： カテゴリー(出荷基準)</t>
+          <t>商品カテゴリ(親カテゴリ)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1811,7 +1833,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 加盟グループ_プロテック（フィラーⅡ含）</t>
+          <t>加盟グループ_プロテック（フィラー2Ⅱ含）</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1855,7 +1877,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of アステック加盟種別(出荷基準)の複製</t>
+          <t>アステック加盟種別</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1943,7 +1965,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of カイゼンReペイントサービス</t>
+          <t>カイゼンReペイント（NULL・空削除）</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1960,7 +1982,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>■ 未応答カード一覧（6件）</t>
+          <t>■ 未応答カード一覧（5件）</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2026,7 @@
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： APS(出荷基準)</t>
+          <t>APS</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2048,7 @@
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>Duplicate of 塗料系統(出荷基準)の複製</t>
+          <t>分類名（リファイン_屋根壁分割）</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2070,7 @@
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： カテゴリー(出荷基準)</t>
+          <t>商品カテゴリ(親カテゴリ)</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2092,7 @@
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>Duplicate of 加盟グループ_プロテック（フィラーⅡ含）</t>
+          <t>加盟グループ_プロテック（フィラー2Ⅱ含）</t>
         </is>
       </c>
     </row>
@@ -2087,34 +2109,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of アステック加盟種別(出荷基準)の複製</t>
+          <t>Duplicate of カイゼンReペイントサービス</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>Duplicate of アステック加盟種別(出荷基準)の複製</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>ER_現場名入り受注</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of カイゼンReペイントサービス</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>Duplicate of カイゼンReペイントサービス</t>
+          <t>カイゼンReペイント（NULL・空削除）</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均）</t>
+          <t>数値進捗（施工店）3ヶ月集計</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント（昨対集計用）</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>元請会社名</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>数値進捗（施工店）3ヶ月集計</t>
+          <t>数値進捗（施工店）</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>元請会社名</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>数値進捗（施工店）</t>
+          <t>契約率（3ヶ月移動平均）</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（昨対集計用）</t>
+          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>施工店分析</t>
+          <t>工場売上分析</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>現場名（工場案件）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>現場名</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>ER_現場名入り売上実績</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>契約率（3ヶ月移動平均）</t>
+          <t>ステータス別_工場・倉庫・施設出荷社数_年比較</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>ER_売上/受注_直近_PRD</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -2636,32 +2636,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>施工店分析</t>
+          <t>工場売上分析</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>現場名（工場案件）</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>現場名</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>ER_現場名入り売上実績</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>契約率（3ヶ月移動平均）</t>
+          <t>商品別_工場・倉庫・施設出荷現場数</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>ER_売上/受注_直近_PRD</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>ステータス別_工場・倉庫・施設出荷社数_年比較</t>
+          <t>ステータス別_工場・倉庫・施設売上</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>商品別_工場・倉庫・施設出荷現場数</t>
+          <t>商品別_工場・倉庫・施設出荷社数</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>ステータス別_工場・倉庫・施設売上</t>
+          <t>ステータス別_工場・倉庫・施設出荷現場数</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>商品別_工場・倉庫・施設出荷社数</t>
+          <t>月別_工場・倉庫・施設出荷社数</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>ER_売上/受注_直近_PRD</t>
+          <t>【大型出荷有無用】ER_売上/受注_直近_PRD</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>ステータス別_工場・倉庫・施設出荷現場数</t>
+          <t>ステータス別_工場・倉庫・施設出荷_平均単価_年比較</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2881,27 +2881,27 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>現場名（工場案件）</t>
+          <t>売上時期</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>現場名</t>
+          <t>売上時期</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
+          <t>ER_売上/受注_直近_PRD</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>工場案件一覧</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
           <t>ER_現場名入り売上実績</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>月別_工場・倉庫・施設出荷社数</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>【大型出荷有無用】ER_売上/受注_直近_PRD</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>ステータス別_工場・倉庫・施設出荷_平均単価_年比較</t>
+          <t>ステータス別_工場・倉庫・施設売上_年比較</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2961,27 +2961,27 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>売上時期</t>
+          <t>現場名（工場案件）</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>売上時期</t>
+          <t>現場名</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
+          <t>ER_現場名入り売上実績</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>ステータス別_工場・倉庫・施設出荷現場数_年比較</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
           <t>ER_売上/受注_直近_PRD</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>工場案件一覧</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>ER_現場名入り売上実績</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>ステータス別_工場・倉庫・施設売上_年比較</t>
+          <t>商品別_工場・倉庫・施設出荷_平均単価</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>ステータス別_工場・倉庫・施設出荷現場数_年比較</t>
+          <t>出荷済社数_工場・施設</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>ER_売上/受注_直近_PRD</t>
+          <t>【大型出荷有無用】ER_売上/受注_直近_PRD</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>商品別_工場・倉庫・施設出荷_平均単価</t>
+          <t>ステータス別_工場・倉庫・施設出荷_平均単価</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>出荷済社数_工場・施設</t>
+          <t>材料別_工場・倉庫・施設売上</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>【大型出荷有無用】ER_売上/受注_直近_PRD</t>
+          <t>ER_売上/受注_直近_PRD</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -3156,17 +3156,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>工場売上分析</t>
+          <t>物件種別修正用</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>現場名（工場案件）</t>
+          <t>コーナン（加盟金なし）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>現場名</t>
+          <t>コーナン（加盟金なし）名</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>ステータス別_工場・倉庫・施設出荷_平均単価</t>
+          <t>物件種別修正用一覧_コラボス</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>ER_売上/受注_直近_PRD</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>工場売上分析</t>
+          <t>物件種別修正用</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>現場名（工場案件）</t>
+          <t>施工店グループ（その他）</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>現場名</t>
+          <t>施工店グループ（その他）</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>材料別_工場・倉庫・施設売上</t>
+          <t>物件種別修正用一覧_コラボス</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>ER_売上/受注_直近_PRD</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金なし）</t>
+          <t>その他の詳細</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金なし）</t>
+          <t>その他"の詳</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>施工店グループ（その他）</t>
+          <t>コーナン（加盟金あり）</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>施工店グループ（その他）</t>
+          <t>コーナン（加盟金あり）名</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -3316,32 +3316,32 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>物件種別修正用</t>
+          <t>完工予測</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>その他の詳細</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>その他"の詳</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>ER_現場名入り売上実績</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>物件種別修正用一覧_コラボス</t>
+          <t>前期 完工粗利進捗（完工・未完工集計）</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>コラボス＋リペイント（日別集計）</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -3356,32 +3356,32 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>物件種別修正用</t>
+          <t>完工予測</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>コーナン（加盟金あり）</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>コーナン（加盟金あり）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>ER_現場名入り売上実績</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>物件種別修正用一覧_コラボス</t>
+          <t>坂本あテスト＿  完工粗利進捗（完工・未完工集計）</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>コラボス＋リペイント（日別集計）</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>前期 完工粗利進捗（完工・未完工集計）</t>
+          <t>月別実績集計表（昨対比較含む）</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>前期 完工粗利進捗（完工・未完工集計）</t>
+          <t>前期 数字進捗集計（案件・見積・契約）</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>坂本あテスト＿  完工粗利進捗（完工・未完工集計）</t>
+          <t>完工粗利進捗（完工・未完工集計）</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>坂本あテスト＿  完工粗利進捗（完工・未完工集計）</t>
+          <t>前期 月別実績集計表（昨対比較含む)</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>月別実績集計表（昨対比較含む）</t>
+          <t>数字進捗集計（案件・見積・契約）</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -3596,17 +3596,17 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>完工予測</t>
+          <t>プロテック案件実績</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>月別実績集計表（昨対比較含む）</t>
+          <t>コラボス_元請会社別新規案件数（昨対比）.</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（日別集計）</t>
+          <t>コラボス＋リペイント（昨対集計用）</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>完工予測</t>
+          <t>プロテック案件実績</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>元請会社名（コラボス）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>前期 数字進捗集計（案件・見積・契約）</t>
+          <t>コラボス_元請会社別新規案件数（昨対比）.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（日別集計）</t>
+          <t>コラボス＋リペイント（昨対集計用）</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>完工予測</t>
+          <t>プロテック案件実績</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>前期 数字進捗集計（案件・見積・契約）</t>
+          <t>コラボス_元請会社別新規案件数（昨対比）.</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（日別集計）</t>
+          <t>コラボス＋リペイント（昨対集計用）</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>完工予測</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>完工粗利進捗（完工・未完工集計）</t>
+          <t>契約率（3ヶ月移動平均/60万円以上）</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（日別集計）</t>
+          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3756,17 +3756,17 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>完工予測</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>完工粗利進捗（完工・未完工集計）</t>
+          <t>契約率（3ヶ月移動平均/60万円以上）</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（日別集計）</t>
+          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -3796,17 +3796,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>完工予測</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>前期 月別実績集計表（昨対比較含む)</t>
+          <t>契約率（12ヶ月移動平均）</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（日別集計）</t>
+          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>完工予測</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>前期 月別実績集計表（昨対比較含む)</t>
+          <t>契約率（12ヶ月移動平均）</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（日別集計）</t>
+          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>完工予測</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>数字進捗集計（案件・見積・契約）</t>
+          <t>契約率（3ヶ月移動平均）</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（日別集計）</t>
+          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>完工予測</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>数字進捗集計（案件・見積・契約）</t>
+          <t>契約率（3ヶ月移動平均）</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（日別集計）</t>
+          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
@@ -3956,17 +3956,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>プロテック案件実績</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>コラボス_元請会社別新規案件数（昨対比）.</t>
+          <t>契約率（12ヶ月移動平均/60万円以上）</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（昨対集計用）</t>
+          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>契約率（3ヶ月移動平均/60万円以上）</t>
+          <t>契約率（12ヶ月移動平均/60万円以上）</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -4036,32 +4036,32 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>元請会社名</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>元請会社（DCMまとめ）</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>コラボス＋リペイント</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>【期待値込】プロテック請負金額集計_元請別（計上予定日基準）</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>契約率（3ヶ月移動平均/60万円以上）</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -4076,32 +4076,32 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>営業担当（コラボス）</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>営業担当（文字化け修正）</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>コラボス＋リペイント</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>【期待値込】プロテック請負金額集計_元請別（計上予定日基準）</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>契約率（3ヶ月移動平均/60万円以上）</t>
-        </is>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均）</t>
+          <t>見積予実_元請別</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4156,32 +4156,32 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均）</t>
+          <t>平均見積金額_元請別(直近1年間)</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均）</t>
+          <t>平均日数_施工店別</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4236,32 +4236,32 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>契約率（3ヶ月移動平均）</t>
+          <t>契約予実_元請別</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>契約率（3ヶ月移動平均）</t>
+          <t>完工予実_元請別</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4316,32 +4316,32 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>契約率（3ヶ月移動平均）</t>
+          <t>施工店請負金額_施工店別（工事完了日基準）</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -4356,32 +4356,32 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均/60万円以上）</t>
+          <t>現調数_施工店別（訪問日基準）</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均/60万円以上）</t>
+          <t>契約予実_担当別</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
@@ -4436,32 +4436,32 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
+          <t>週間MTG用コラボス分析</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>実績・期待値</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>実績判断</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均/60万円以上）</t>
+          <t>対応案件数_施工店別（見積提案日基準）</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4481,27 +4481,27 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>実績・期待値</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>実績判断</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>【期待値込】プロテック請負金額集計_元請別（計上予定日基準）</t>
+          <t>契約数_施工店別（結果確定日基準）</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>コラボス＋リペイント</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>見積予実_元請別</t>
+          <t>見積予実_担当別</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>平均見積金額_元請別(直近1年間)</t>
+          <t>完工予実_元請別（注力外）</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>平均日数_施工店別</t>
+          <t>完工予実_担当別</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>契約予実_元請別</t>
+          <t>平均見積金額_元請別(直近3ヶ月)</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>完工予実_元請別</t>
+          <t>プロテック請負金額集計_担当別</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -4716,32 +4716,32 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>週間MTG用コラボス分析</t>
+          <t>法人営業部用_売上集計(出荷日基準)</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>実績・期待値</t>
+          <t>Duplicate of 次の複製： APS(出荷基準)</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>実績判断</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>ER_受注/出荷_直近_PRD</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>施工店請負金額_施工店別（工事完了日基準）</t>
+          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>ER_現場名入り受注</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -4756,32 +4756,32 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>週間MTG用コラボス分析</t>
+          <t>法人営業部用_売上集計(出荷日基準)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>実績・期待値</t>
+          <t>Duplicate of 塗料系統(出荷基準)の複製</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>実績判断</t>
+          <t>分類名（リファイン_屋根壁分割）</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>ER_受注/出荷_直近_PRD</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>現調数_施工店別（訪問日基準）</t>
+          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>ER_現場名入り受注</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -4796,32 +4796,32 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>週間MTG用コラボス分析</t>
+          <t>法人営業部用_売上集計(出荷日基準)</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>実績・期待値</t>
+          <t>Duplicate of 次の複製： カテゴリー(出荷基準)</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>実績判断</t>
+          <t>商品カテゴリ(親カテゴリ)</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>ER_受注/出荷_直近_PRD</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>契約予実_担当別</t>
+          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>ER_現場名入り受注</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>週間MTG用コラボス分析</t>
+          <t>法人営業部用_売上集計(出荷日基準)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>実績・期待値</t>
+          <t>Duplicate of 加盟グループ_プロテック（フィラーⅡ含）</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>実績判断</t>
+          <t>加盟グループ_プロテック（フィラー2Ⅱ含）</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>ER_受注/出荷_直近_PRD</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>対応案件数_施工店別（見積提案日基準）</t>
+          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>ER_現場名入り受注</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -4876,32 +4876,32 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>週間MTG用コラボス分析</t>
+          <t>法人営業部用_売上集計(出荷日基準)</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>実績・期待値</t>
+          <t>Duplicate of カイゼンReペイントサービス</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>実績判断</t>
+          <t>カイゼンReペイント（NULL・空削除）</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>ER_受注/出荷_直近_PRD</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>契約数_施工店別（結果確定日基準）</t>
+          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント</t>
+          <t>ER_現場名入り受注</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -4910,448 +4910,8 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>週間MTG用コラボス分析</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>実績・期待値</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>実績判断</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>見積予実_担当別</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>週間MTG用コラボス分析</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>実績・期待値</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr">
-        <is>
-          <t>実績判断</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>完工予実_元請別（注力外）</t>
-        </is>
-      </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>週間MTG用コラボス分析</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>実績・期待値</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>実績判断</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>完工予実_担当別</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t>週間MTG用コラボス分析</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>実績・期待値</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>実績判断</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>平均見積金額_元請別(直近3ヶ月)</t>
-        </is>
-      </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>週間MTG用コラボス分析</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>実績・期待値</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>実績判断</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>プロテック請負金額集計_担当別</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t>法人営業部用_売上集計(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="C75" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： APS(出荷基準)</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： APS(出荷基準)</t>
-        </is>
-      </c>
-      <c r="E75" s="12" t="inlineStr">
-        <is>
-          <t>ER_受注/出荷_直近_PRD</t>
-        </is>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="G75" s="12" t="inlineStr">
-        <is>
-          <t>ER_現場名入り受注</t>
-        </is>
-      </c>
-      <c r="H75" s="11" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>法人営業部用_売上集計(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate of 塗料系統(出荷基準)の複製</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate of 塗料系統(出荷基準)の複製</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>ER_受注/出荷_直近_PRD</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>ER_現場名入り受注</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>法人営業部用_売上集計(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： カテゴリー(出荷基準)</t>
-        </is>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： カテゴリー(出荷基準)</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>ER_受注/出荷_直近_PRD</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="G77" s="12" t="inlineStr">
-        <is>
-          <t>ER_現場名入り受注</t>
-        </is>
-      </c>
-      <c r="H77" s="11" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>法人営業部用_売上集計(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate of 加盟グループ_プロテック（フィラーⅡ含）</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate of 加盟グループ_プロテック（フィラーⅡ含）</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>ER_受注/出荷_直近_PRD</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>ER_現場名入り受注</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>法人営業部用_売上集計(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of アステック加盟種別(出荷基準)の複製</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of アステック加盟種別(出荷基準)の複製</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>ER_受注/出荷_直近_PRD</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="G79" s="12" t="inlineStr">
-        <is>
-          <t>ER_現場名入り受注</t>
-        </is>
-      </c>
-      <c r="H79" s="11" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>法人営業部用_売上集計(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate of カイゼンReペイントサービス</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate of カイゼンReペイントサービス</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>ER_受注/出荷_直近_PRD</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate of 次の複製： 売上詳細(出荷日基準)</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>ER_現場名入り受注</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>❌ カラム無し</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H80"/>
+  <autoFilter ref="A1:H69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5474,7 +5034,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -5514,7 +5074,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -5554,7 +5114,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -5634,7 +5194,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -5674,7 +5234,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -5714,7 +5274,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -5794,7 +5354,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -5834,7 +5394,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -5874,7 +5434,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -5954,7 +5514,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -5994,7 +5554,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -6034,7 +5594,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -6114,7 +5674,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -6154,7 +5714,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -6194,7 +5754,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -6274,7 +5834,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -6314,7 +5874,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -6354,7 +5914,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6434,7 +5994,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -6474,7 +6034,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -6514,7 +6074,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -6594,7 +6154,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -6634,7 +6194,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -6674,7 +6234,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -6687,14 +6247,14 @@
           <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6314,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -6794,7 +6354,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -6834,7 +6394,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -6914,7 +6474,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -6954,7 +6514,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -6994,7 +6554,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7074,7 +6634,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -7114,7 +6674,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -7154,7 +6714,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -7234,7 +6794,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -7274,7 +6834,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -7314,7 +6874,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -7394,7 +6954,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -7434,7 +6994,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -7474,7 +7034,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -7554,7 +7114,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -7594,7 +7154,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -7634,7 +7194,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -7714,7 +7274,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -7754,7 +7314,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -7794,7 +7354,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -7874,7 +7434,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -7914,7 +7474,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -7954,7 +7514,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -8034,7 +7594,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -8074,7 +7634,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -8114,7 +7674,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -8194,7 +7754,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -8234,7 +7794,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -8274,7 +7834,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -8354,7 +7914,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -8394,7 +7954,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -8434,7 +7994,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -8514,7 +8074,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -8554,7 +8114,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -8594,7 +8154,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -8674,7 +8234,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -8714,7 +8274,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -8754,7 +8314,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -8834,7 +8394,7 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -8874,7 +8434,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -8914,7 +8474,7 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -8994,7 +8554,7 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -9034,7 +8594,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -9074,7 +8634,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -9087,14 +8647,14 @@
           <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -9154,7 +8714,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -9194,7 +8754,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -9234,7 +8794,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -9314,7 +8874,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -9354,7 +8914,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -9394,7 +8954,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -12234,7 +11794,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金なし）</t>
+          <t>コーナン（加盟金なし）名</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -12354,7 +11914,7 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金あり）</t>
+          <t>コーナン（加盟金あり）名</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -12394,7 +11954,7 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金なし）</t>
+          <t>コーナン（加盟金なし）名</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -12514,7 +12074,7 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金あり）</t>
+          <t>コーナン（加盟金あり）名</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -12554,7 +12114,7 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金なし）</t>
+          <t>コーナン（加盟金なし）名</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -12674,7 +12234,7 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金あり）</t>
+          <t>コーナン（加盟金あり）名</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -12714,7 +12274,7 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -12754,7 +12314,7 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -12794,7 +12354,7 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -12807,14 +12367,14 @@
           <t>コラボス＋リペイント（日別集計）</t>
         </is>
       </c>
-      <c r="G186" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G186" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12394,7 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -12874,7 +12434,7 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
@@ -12914,7 +12474,7 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
@@ -12954,7 +12514,7 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
@@ -12994,7 +12554,7 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
@@ -13034,7 +12594,7 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
@@ -13074,7 +12634,7 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
@@ -13114,7 +12674,7 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
@@ -13154,7 +12714,7 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
@@ -13167,14 +12727,14 @@
           <t>コラボス＋リペイント（日別集計）</t>
         </is>
       </c>
-      <c r="G195" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G195" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -13194,7 +12754,7 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -13234,7 +12794,7 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -13274,7 +12834,7 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13314,7 +12874,7 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13354,7 +12914,7 @@
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13394,7 +12954,7 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13407,14 +12967,14 @@
           <t>コラボス＋リペイント（日別集計）</t>
         </is>
       </c>
-      <c r="G201" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G201" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H201" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -13434,7 +12994,7 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13474,7 +13034,7 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13514,7 +13074,7 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -13527,14 +13087,14 @@
           <t>コラボス＋リペイント（日別集計）</t>
         </is>
       </c>
-      <c r="G204" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G204" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13114,7 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -13594,7 +13154,7 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -13634,7 +13194,7 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -13674,7 +13234,7 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -13714,7 +13274,7 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -13754,7 +13314,7 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -13767,14 +13327,14 @@
           <t>コラボス＋リペイント（日別集計）</t>
         </is>
       </c>
-      <c r="G210" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G210" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13354,7 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -13834,7 +13394,7 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -13874,7 +13434,7 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -13887,14 +13447,14 @@
           <t>コラボス＋リペイント（日別集計）</t>
         </is>
       </c>
-      <c r="G213" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G213" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13474,7 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -13954,7 +13514,7 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
@@ -13994,7 +13554,7 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -14034,7 +13594,7 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
@@ -14074,7 +13634,7 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -14114,7 +13674,7 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -14154,7 +13714,7 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
@@ -14194,7 +13754,7 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
@@ -14234,7 +13794,7 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -14274,7 +13834,7 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
@@ -14314,7 +13874,7 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
@@ -14354,7 +13914,7 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
@@ -14367,14 +13927,14 @@
           <t>コラボス＋リペイント（日別集計）</t>
         </is>
       </c>
-      <c r="G225" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G225" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -14394,7 +13954,7 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -14434,7 +13994,7 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
@@ -14474,7 +14034,7 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
@@ -14514,7 +14074,7 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
@@ -14554,7 +14114,7 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
@@ -14594,7 +14154,7 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
@@ -14634,7 +14194,7 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
@@ -14674,7 +14234,7 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
@@ -14714,7 +14274,7 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -14754,7 +14314,7 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -14794,7 +14354,7 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
@@ -14834,7 +14394,7 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
@@ -14874,7 +14434,7 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
@@ -14914,7 +14474,7 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
@@ -14954,7 +14514,7 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
@@ -14994,7 +14554,7 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
@@ -15034,7 +14594,7 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
@@ -15074,7 +14634,7 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
@@ -15114,7 +14674,7 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
@@ -15154,7 +14714,7 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
@@ -15194,7 +14754,7 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
@@ -15234,7 +14794,7 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
@@ -15274,7 +14834,7 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
@@ -15314,7 +14874,7 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
@@ -15354,7 +14914,7 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
@@ -15394,7 +14954,7 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
@@ -15434,7 +14994,7 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
@@ -15474,7 +15034,7 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
@@ -15514,7 +15074,7 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
@@ -15554,7 +15114,7 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
@@ -15594,7 +15154,7 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
@@ -15634,7 +15194,7 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
@@ -15674,7 +15234,7 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
@@ -15714,7 +15274,7 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
@@ -15754,7 +15314,7 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
@@ -15794,7 +15354,7 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
@@ -15834,7 +15394,7 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
@@ -15874,7 +15434,7 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
@@ -15914,7 +15474,7 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
@@ -15954,7 +15514,7 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
@@ -15994,7 +15554,7 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -16034,7 +15594,7 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
@@ -16074,7 +15634,7 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -16114,7 +15674,7 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -16154,7 +15714,7 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -16194,7 +15754,7 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -16234,7 +15794,7 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -16274,7 +15834,7 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
@@ -16314,7 +15874,7 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
@@ -16354,7 +15914,7 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
@@ -16367,14 +15927,14 @@
           <t>コラボス＋リペイント（昨対集計用）</t>
         </is>
       </c>
-      <c r="G275" s="13" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="G275" s="14" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>カラム有り</t>
+          <t>カラム無し</t>
         </is>
       </c>
     </row>
@@ -16394,7 +15954,7 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
@@ -16407,14 +15967,14 @@
           <t>コラボス＋リペイント（昨対集計用）</t>
         </is>
       </c>
-      <c r="G276" s="13" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="G276" s="14" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>カラム有り</t>
+          <t>カラム無し</t>
         </is>
       </c>
     </row>
@@ -16434,7 +15994,7 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
@@ -16474,7 +16034,7 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
@@ -16514,7 +16074,7 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
@@ -16554,7 +16114,7 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
@@ -16594,7 +16154,7 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
@@ -16634,7 +16194,7 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
@@ -16674,7 +16234,7 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
@@ -16714,7 +16274,7 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
@@ -16754,7 +16314,7 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
@@ -16794,7 +16354,7 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
@@ -16834,7 +16394,7 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
@@ -16874,7 +16434,7 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
@@ -16914,7 +16474,7 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
@@ -16954,7 +16514,7 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
@@ -16994,7 +16554,7 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
@@ -19114,7 +18674,7 @@
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E344" s="5" t="inlineStr">
@@ -19194,7 +18754,7 @@
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E346" s="5" t="inlineStr">
@@ -19234,7 +18794,7 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E347" s="5" t="inlineStr">
@@ -19274,7 +18834,7 @@
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E348" s="5" t="inlineStr">
@@ -19354,7 +18914,7 @@
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E350" s="5" t="inlineStr">
@@ -19394,7 +18954,7 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E351" s="5" t="inlineStr">
@@ -19434,7 +18994,7 @@
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E352" s="5" t="inlineStr">
@@ -19514,7 +19074,7 @@
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E354" s="5" t="inlineStr">
@@ -19554,7 +19114,7 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E355" s="5" t="inlineStr">
@@ -19594,7 +19154,7 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E356" s="5" t="inlineStr">
@@ -19674,7 +19234,7 @@
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E358" s="5" t="inlineStr">
@@ -19714,7 +19274,7 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E359" s="5" t="inlineStr">
@@ -19754,7 +19314,7 @@
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E360" s="5" t="inlineStr">
@@ -19834,7 +19394,7 @@
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E362" s="5" t="inlineStr">
@@ -19874,7 +19434,7 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E363" s="5" t="inlineStr">
@@ -19914,7 +19474,7 @@
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E364" s="5" t="inlineStr">
@@ -19994,7 +19554,7 @@
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E366" s="5" t="inlineStr">
@@ -20034,7 +19594,7 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E367" s="5" t="inlineStr">
@@ -20074,7 +19634,7 @@
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E368" s="5" t="inlineStr">
@@ -20154,7 +19714,7 @@
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E370" s="5" t="inlineStr">
@@ -20194,7 +19754,7 @@
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E371" s="5" t="inlineStr">
@@ -20234,7 +19794,7 @@
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E372" s="5" t="inlineStr">
@@ -20314,7 +19874,7 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E374" s="5" t="inlineStr">
@@ -20354,7 +19914,7 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E375" s="5" t="inlineStr">
@@ -20394,7 +19954,7 @@
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E376" s="5" t="inlineStr">
@@ -20474,7 +20034,7 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E378" s="5" t="inlineStr">
@@ -20514,7 +20074,7 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E379" s="5" t="inlineStr">
@@ -20554,7 +20114,7 @@
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E380" s="5" t="inlineStr">
@@ -20634,7 +20194,7 @@
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E382" s="5" t="inlineStr">
@@ -20674,7 +20234,7 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E383" s="5" t="inlineStr">
@@ -20714,7 +20274,7 @@
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E384" s="5" t="inlineStr">
@@ -20794,7 +20354,7 @@
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E386" s="5" t="inlineStr">
@@ -20834,7 +20394,7 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E387" s="5" t="inlineStr">
@@ -20874,7 +20434,7 @@
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E388" s="5" t="inlineStr">
@@ -20954,7 +20514,7 @@
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E390" s="5" t="inlineStr">
@@ -20994,7 +20554,7 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E391" s="5" t="inlineStr">
@@ -21034,7 +20594,7 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E392" s="5" t="inlineStr">
@@ -21114,7 +20674,7 @@
       </c>
       <c r="D394" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E394" s="5" t="inlineStr">
@@ -21154,7 +20714,7 @@
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E395" s="5" t="inlineStr">
@@ -21194,7 +20754,7 @@
       </c>
       <c r="D396" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E396" s="5" t="inlineStr">
@@ -21274,7 +20834,7 @@
       </c>
       <c r="D398" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E398" s="5" t="inlineStr">
@@ -21314,7 +20874,7 @@
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E399" s="5" t="inlineStr">
@@ -21354,7 +20914,7 @@
       </c>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E400" s="5" t="inlineStr">
@@ -21434,7 +20994,7 @@
       </c>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E402" s="5" t="inlineStr">
@@ -21474,7 +21034,7 @@
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E403" s="5" t="inlineStr">
@@ -21514,7 +21074,7 @@
       </c>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E404" s="5" t="inlineStr">
@@ -21594,7 +21154,7 @@
       </c>
       <c r="D406" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E406" s="5" t="inlineStr">
@@ -21634,7 +21194,7 @@
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E407" s="5" t="inlineStr">
@@ -21674,7 +21234,7 @@
       </c>
       <c r="D408" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E408" s="5" t="inlineStr">
@@ -21754,7 +21314,7 @@
       </c>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E410" s="5" t="inlineStr">
@@ -21794,7 +21354,7 @@
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E411" s="5" t="inlineStr">
@@ -21834,7 +21394,7 @@
       </c>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E412" s="5" t="inlineStr">
@@ -21914,7 +21474,7 @@
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E414" s="5" t="inlineStr">
@@ -21954,7 +21514,7 @@
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E415" s="5" t="inlineStr">
@@ -21994,7 +21554,7 @@
       </c>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E416" s="5" t="inlineStr">
@@ -22034,7 +21594,7 @@
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E417" s="5" t="inlineStr">
@@ -22074,7 +21634,7 @@
       </c>
       <c r="D418" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E418" s="5" t="inlineStr">
@@ -22114,7 +21674,7 @@
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E419" s="5" t="inlineStr">
@@ -22154,7 +21714,7 @@
       </c>
       <c r="D420" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E420" s="5" t="inlineStr">
@@ -22194,7 +21754,7 @@
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E421" s="5" t="inlineStr">
@@ -22234,7 +21794,7 @@
       </c>
       <c r="D422" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E422" s="5" t="inlineStr">
@@ -22274,7 +21834,7 @@
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E423" s="5" t="inlineStr">
@@ -22314,7 +21874,7 @@
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E424" s="5" t="inlineStr">
@@ -22354,7 +21914,7 @@
       </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E425" s="5" t="inlineStr">
@@ -22394,7 +21954,7 @@
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E426" s="5" t="inlineStr">
@@ -22434,7 +21994,7 @@
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E427" s="5" t="inlineStr">
@@ -22474,7 +22034,7 @@
       </c>
       <c r="D428" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E428" s="5" t="inlineStr">
@@ -22514,7 +22074,7 @@
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E429" s="5" t="inlineStr">
@@ -22554,7 +22114,7 @@
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E430" s="5" t="inlineStr">
@@ -22594,7 +22154,7 @@
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E431" s="5" t="inlineStr">
@@ -22634,7 +22194,7 @@
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E432" s="5" t="inlineStr">
@@ -22674,7 +22234,7 @@
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E433" s="5" t="inlineStr">
@@ -22714,7 +22274,7 @@
       </c>
       <c r="D434" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E434" s="5" t="inlineStr">
@@ -22754,7 +22314,7 @@
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E435" s="5" t="inlineStr">
@@ -22794,7 +22354,7 @@
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E436" s="5" t="inlineStr">
@@ -22834,7 +22394,7 @@
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E437" s="5" t="inlineStr">
@@ -22874,7 +22434,7 @@
       </c>
       <c r="D438" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E438" s="5" t="inlineStr">
@@ -22914,7 +22474,7 @@
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E439" s="5" t="inlineStr">
@@ -22954,7 +22514,7 @@
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E440" s="5" t="inlineStr">
@@ -22994,7 +22554,7 @@
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E441" s="5" t="inlineStr">
@@ -23034,7 +22594,7 @@
       </c>
       <c r="D442" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E442" s="5" t="inlineStr">
@@ -23074,7 +22634,7 @@
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E443" s="5" t="inlineStr">
@@ -23114,7 +22674,7 @@
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E444" s="5" t="inlineStr">
@@ -23154,7 +22714,7 @@
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E445" s="5" t="inlineStr">
@@ -23194,7 +22754,7 @@
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E446" s="5" t="inlineStr">
@@ -23234,7 +22794,7 @@
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E447" s="5" t="inlineStr">
@@ -23274,7 +22834,7 @@
       </c>
       <c r="D448" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E448" s="5" t="inlineStr">
@@ -23314,7 +22874,7 @@
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E449" s="5" t="inlineStr">
@@ -23354,7 +22914,7 @@
       </c>
       <c r="D450" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E450" s="5" t="inlineStr">
@@ -23394,7 +22954,7 @@
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E451" s="5" t="inlineStr">
@@ -23434,7 +22994,7 @@
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E452" s="5" t="inlineStr">
@@ -23474,7 +23034,7 @@
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E453" s="5" t="inlineStr">
@@ -23514,7 +23074,7 @@
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E454" s="5" t="inlineStr">
@@ -23554,7 +23114,7 @@
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E455" s="5" t="inlineStr">
@@ -23594,7 +23154,7 @@
       </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E456" s="5" t="inlineStr">
@@ -23634,7 +23194,7 @@
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E457" s="5" t="inlineStr">
@@ -23674,7 +23234,7 @@
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E458" s="5" t="inlineStr">
@@ -23714,7 +23274,7 @@
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E459" s="5" t="inlineStr">
@@ -23754,7 +23314,7 @@
       </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E460" s="5" t="inlineStr">
@@ -23794,7 +23354,7 @@
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E461" s="5" t="inlineStr">
@@ -23834,7 +23394,7 @@
       </c>
       <c r="D462" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E462" s="5" t="inlineStr">
@@ -23874,7 +23434,7 @@
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E463" s="5" t="inlineStr">
@@ -23914,7 +23474,7 @@
       </c>
       <c r="D464" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E464" s="5" t="inlineStr">
@@ -23954,7 +23514,7 @@
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E465" s="5" t="inlineStr">
@@ -23994,7 +23554,7 @@
       </c>
       <c r="D466" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E466" s="5" t="inlineStr">
@@ -24034,7 +23594,7 @@
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E467" s="5" t="inlineStr">
@@ -24074,7 +23634,7 @@
       </c>
       <c r="D468" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E468" s="5" t="inlineStr">
@@ -24114,7 +23674,7 @@
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E469" s="5" t="inlineStr">
@@ -24154,7 +23714,7 @@
       </c>
       <c r="D470" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E470" s="5" t="inlineStr">
@@ -24194,7 +23754,7 @@
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E471" s="5" t="inlineStr">
@@ -24234,7 +23794,7 @@
       </c>
       <c r="D472" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E472" s="5" t="inlineStr">
@@ -24274,7 +23834,7 @@
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E473" s="5" t="inlineStr">
@@ -24314,7 +23874,7 @@
       </c>
       <c r="D474" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="E474" s="5" t="inlineStr">
@@ -24354,7 +23914,7 @@
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="E475" s="5" t="inlineStr">
@@ -24394,7 +23954,7 @@
       </c>
       <c r="D476" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E476" s="5" t="inlineStr">
@@ -24434,7 +23994,7 @@
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E477" s="5" t="inlineStr">
@@ -24514,7 +24074,7 @@
       </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E479" s="5" t="inlineStr">
@@ -24594,7 +24154,7 @@
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E481" s="5" t="inlineStr">
@@ -24634,7 +24194,7 @@
       </c>
       <c r="D482" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E482" s="5" t="inlineStr">
@@ -24714,7 +24274,7 @@
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E484" s="5" t="inlineStr">
@@ -24794,7 +24354,7 @@
       </c>
       <c r="D486" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E486" s="5" t="inlineStr">
@@ -24834,7 +24394,7 @@
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E487" s="5" t="inlineStr">
@@ -24914,7 +24474,7 @@
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E489" s="5" t="inlineStr">
@@ -24994,7 +24554,7 @@
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E491" s="5" t="inlineStr">
@@ -25034,7 +24594,7 @@
       </c>
       <c r="D492" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E492" s="5" t="inlineStr">
@@ -25114,7 +24674,7 @@
       </c>
       <c r="D494" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E494" s="5" t="inlineStr">
@@ -25194,7 +24754,7 @@
       </c>
       <c r="D496" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E496" s="5" t="inlineStr">
@@ -25234,7 +24794,7 @@
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E497" s="5" t="inlineStr">
@@ -25314,7 +24874,7 @@
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E499" s="5" t="inlineStr">
@@ -25394,7 +24954,7 @@
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E501" s="5" t="inlineStr">
@@ -25434,7 +24994,7 @@
       </c>
       <c r="D502" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E502" s="5" t="inlineStr">
@@ -25514,7 +25074,7 @@
       </c>
       <c r="D504" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E504" s="5" t="inlineStr">
@@ -25527,14 +25087,14 @@
           <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
-      <c r="G504" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G504" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H504" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25154,7 @@
       </c>
       <c r="D506" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E506" s="5" t="inlineStr">
@@ -25634,7 +25194,7 @@
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E507" s="5" t="inlineStr">
@@ -25714,7 +25274,7 @@
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E509" s="5" t="inlineStr">
@@ -25794,7 +25354,7 @@
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E511" s="5" t="inlineStr">
@@ -25834,7 +25394,7 @@
       </c>
       <c r="D512" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E512" s="5" t="inlineStr">
@@ -25914,7 +25474,7 @@
       </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E514" s="5" t="inlineStr">
@@ -25994,7 +25554,7 @@
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E516" s="5" t="inlineStr">
@@ -26034,7 +25594,7 @@
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E517" s="5" t="inlineStr">
@@ -26114,7 +25674,7 @@
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E519" s="5" t="inlineStr">
@@ -26194,7 +25754,7 @@
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E521" s="5" t="inlineStr">
@@ -26234,7 +25794,7 @@
       </c>
       <c r="D522" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E522" s="5" t="inlineStr">
@@ -26314,7 +25874,7 @@
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E524" s="5" t="inlineStr">
@@ -26327,14 +25887,14 @@
           <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
-      <c r="G524" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G524" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H524" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -26394,7 +25954,7 @@
       </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E526" s="5" t="inlineStr">
@@ -26434,7 +25994,7 @@
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E527" s="5" t="inlineStr">
@@ -26514,7 +26074,7 @@
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E529" s="5" t="inlineStr">
@@ -26594,7 +26154,7 @@
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E531" s="5" t="inlineStr">
@@ -26634,7 +26194,7 @@
       </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E532" s="5" t="inlineStr">
@@ -26714,7 +26274,7 @@
       </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E534" s="5" t="inlineStr">
@@ -26794,7 +26354,7 @@
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E536" s="5" t="inlineStr">
@@ -26834,7 +26394,7 @@
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E537" s="5" t="inlineStr">
@@ -26914,7 +26474,7 @@
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E539" s="5" t="inlineStr">
@@ -26994,7 +26554,7 @@
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E541" s="5" t="inlineStr">
@@ -27034,7 +26594,7 @@
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E542" s="5" t="inlineStr">
@@ -27114,7 +26674,7 @@
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E544" s="5" t="inlineStr">
@@ -27194,7 +26754,7 @@
       </c>
       <c r="D546" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E546" s="5" t="inlineStr">
@@ -27234,7 +26794,7 @@
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E547" s="5" t="inlineStr">
@@ -27314,7 +26874,7 @@
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E549" s="5" t="inlineStr">
@@ -27394,7 +26954,7 @@
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E551" s="5" t="inlineStr">
@@ -27434,7 +26994,7 @@
       </c>
       <c r="D552" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E552" s="5" t="inlineStr">
@@ -27514,7 +27074,7 @@
       </c>
       <c r="D554" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E554" s="5" t="inlineStr">
@@ -27594,7 +27154,7 @@
       </c>
       <c r="D556" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E556" s="5" t="inlineStr">
@@ -27634,7 +27194,7 @@
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E557" s="5" t="inlineStr">
@@ -27714,7 +27274,7 @@
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E559" s="5" t="inlineStr">
@@ -27794,7 +27354,7 @@
       </c>
       <c r="D561" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E561" s="5" t="inlineStr">
@@ -27834,7 +27394,7 @@
       </c>
       <c r="D562" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E562" s="5" t="inlineStr">
@@ -27914,7 +27474,7 @@
       </c>
       <c r="D564" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E564" s="5" t="inlineStr">
@@ -27927,14 +27487,14 @@
           <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
-      <c r="G564" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G564" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H564" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -27994,7 +27554,7 @@
       </c>
       <c r="D566" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E566" s="5" t="inlineStr">
@@ -28034,7 +27594,7 @@
       </c>
       <c r="D567" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E567" s="5" t="inlineStr">
@@ -28114,7 +27674,7 @@
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E569" s="5" t="inlineStr">
@@ -28194,7 +27754,7 @@
       </c>
       <c r="D571" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E571" s="5" t="inlineStr">
@@ -28234,7 +27794,7 @@
       </c>
       <c r="D572" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E572" s="5" t="inlineStr">
@@ -28314,7 +27874,7 @@
       </c>
       <c r="D574" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E574" s="5" t="inlineStr">
@@ -28394,7 +27954,7 @@
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E576" s="5" t="inlineStr">
@@ -28434,7 +27994,7 @@
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E577" s="5" t="inlineStr">
@@ -28514,7 +28074,7 @@
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E579" s="5" t="inlineStr">
@@ -28594,7 +28154,7 @@
       </c>
       <c r="D581" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E581" s="5" t="inlineStr">
@@ -28634,7 +28194,7 @@
       </c>
       <c r="D582" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E582" s="5" t="inlineStr">
@@ -28714,7 +28274,7 @@
       </c>
       <c r="D584" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E584" s="5" t="inlineStr">
@@ -28794,7 +28354,7 @@
       </c>
       <c r="D586" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E586" s="5" t="inlineStr">
@@ -28834,7 +28394,7 @@
       </c>
       <c r="D587" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E587" s="5" t="inlineStr">
@@ -28914,7 +28474,7 @@
       </c>
       <c r="D589" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E589" s="5" t="inlineStr">
@@ -28994,7 +28554,7 @@
       </c>
       <c r="D591" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E591" s="5" t="inlineStr">
@@ -29034,7 +28594,7 @@
       </c>
       <c r="D592" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E592" s="5" t="inlineStr">
@@ -29114,7 +28674,7 @@
       </c>
       <c r="D594" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E594" s="5" t="inlineStr">
@@ -29194,7 +28754,7 @@
       </c>
       <c r="D596" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E596" s="5" t="inlineStr">
@@ -29234,7 +28794,7 @@
       </c>
       <c r="D597" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E597" s="5" t="inlineStr">
@@ -29314,7 +28874,7 @@
       </c>
       <c r="D599" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E599" s="5" t="inlineStr">
@@ -29394,7 +28954,7 @@
       </c>
       <c r="D601" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E601" s="5" t="inlineStr">
@@ -29434,7 +28994,7 @@
       </c>
       <c r="D602" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E602" s="5" t="inlineStr">
@@ -29514,7 +29074,7 @@
       </c>
       <c r="D604" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E604" s="5" t="inlineStr">
@@ -29594,7 +29154,7 @@
       </c>
       <c r="D606" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E606" s="5" t="inlineStr">
@@ -29634,7 +29194,7 @@
       </c>
       <c r="D607" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E607" s="5" t="inlineStr">
@@ -29714,7 +29274,7 @@
       </c>
       <c r="D609" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E609" s="5" t="inlineStr">
@@ -29794,7 +29354,7 @@
       </c>
       <c r="D611" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E611" s="5" t="inlineStr">
@@ -29834,7 +29394,7 @@
       </c>
       <c r="D612" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E612" s="5" t="inlineStr">
@@ -29914,7 +29474,7 @@
       </c>
       <c r="D614" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E614" s="5" t="inlineStr">
@@ -29927,14 +29487,14 @@
           <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
-      <c r="G614" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G614" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H614" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29554,7 @@
       </c>
       <c r="D616" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E616" s="5" t="inlineStr">
@@ -30034,7 +29594,7 @@
       </c>
       <c r="D617" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E617" s="5" t="inlineStr">
@@ -30114,7 +29674,7 @@
       </c>
       <c r="D619" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E619" s="5" t="inlineStr">
@@ -30194,7 +29754,7 @@
       </c>
       <c r="D621" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E621" s="5" t="inlineStr">
@@ -30234,7 +29794,7 @@
       </c>
       <c r="D622" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E622" s="5" t="inlineStr">
@@ -30314,7 +29874,7 @@
       </c>
       <c r="D624" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E624" s="5" t="inlineStr">
@@ -30394,7 +29954,7 @@
       </c>
       <c r="D626" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E626" s="5" t="inlineStr">
@@ -30434,7 +29994,7 @@
       </c>
       <c r="D627" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E627" s="5" t="inlineStr">
@@ -30514,7 +30074,7 @@
       </c>
       <c r="D629" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E629" s="5" t="inlineStr">
@@ -30594,7 +30154,7 @@
       </c>
       <c r="D631" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E631" s="5" t="inlineStr">
@@ -30634,7 +30194,7 @@
       </c>
       <c r="D632" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E632" s="5" t="inlineStr">
@@ -30714,7 +30274,7 @@
       </c>
       <c r="D634" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E634" s="5" t="inlineStr">
@@ -30794,7 +30354,7 @@
       </c>
       <c r="D636" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E636" s="5" t="inlineStr">
@@ -30834,7 +30394,7 @@
       </c>
       <c r="D637" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E637" s="5" t="inlineStr">
@@ -30914,7 +30474,7 @@
       </c>
       <c r="D639" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E639" s="5" t="inlineStr">
@@ -30994,7 +30554,7 @@
       </c>
       <c r="D641" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E641" s="5" t="inlineStr">
@@ -31034,7 +30594,7 @@
       </c>
       <c r="D642" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E642" s="5" t="inlineStr">
@@ -31114,7 +30674,7 @@
       </c>
       <c r="D644" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E644" s="5" t="inlineStr">
@@ -31194,7 +30754,7 @@
       </c>
       <c r="D646" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E646" s="5" t="inlineStr">
@@ -31234,7 +30794,7 @@
       </c>
       <c r="D647" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E647" s="5" t="inlineStr">
@@ -31314,7 +30874,7 @@
       </c>
       <c r="D649" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E649" s="5" t="inlineStr">
@@ -31394,7 +30954,7 @@
       </c>
       <c r="D651" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E651" s="5" t="inlineStr">
@@ -31434,7 +30994,7 @@
       </c>
       <c r="D652" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="E652" s="5" t="inlineStr">
@@ -31514,7 +31074,7 @@
       </c>
       <c r="D654" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E654" s="5" t="inlineStr">
@@ -31674,7 +31234,7 @@
       </c>
       <c r="D658" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E658" s="5" t="inlineStr">
@@ -31714,7 +31274,7 @@
       </c>
       <c r="D659" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E659" s="5" t="inlineStr">
@@ -31727,14 +31287,14 @@
           <t>コラボス集計</t>
         </is>
       </c>
-      <c r="G659" s="13" t="inlineStr">
-        <is>
-          <t>✅</t>
+      <c r="G659" s="14" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
       <c r="H659" s="5" t="inlineStr">
         <is>
-          <t>カラム有り</t>
+          <t>カラム無し</t>
         </is>
       </c>
     </row>
@@ -31874,7 +31434,7 @@
       </c>
       <c r="D663" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E663" s="5" t="inlineStr">
@@ -31914,7 +31474,7 @@
       </c>
       <c r="D664" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E664" s="5" t="inlineStr">
@@ -32074,7 +31634,7 @@
       </c>
       <c r="D668" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E668" s="5" t="inlineStr">
@@ -32114,7 +31674,7 @@
       </c>
       <c r="D669" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E669" s="5" t="inlineStr">
@@ -32274,7 +31834,7 @@
       </c>
       <c r="D673" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E673" s="5" t="inlineStr">
@@ -32314,7 +31874,7 @@
       </c>
       <c r="D674" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E674" s="5" t="inlineStr">
@@ -32474,7 +32034,7 @@
       </c>
       <c r="D678" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E678" s="5" t="inlineStr">
@@ -32514,7 +32074,7 @@
       </c>
       <c r="D679" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E679" s="5" t="inlineStr">
@@ -32674,7 +32234,7 @@
       </c>
       <c r="D683" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E683" s="5" t="inlineStr">
@@ -32714,7 +32274,7 @@
       </c>
       <c r="D684" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E684" s="5" t="inlineStr">
@@ -32874,7 +32434,7 @@
       </c>
       <c r="D688" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E688" s="5" t="inlineStr">
@@ -32914,7 +32474,7 @@
       </c>
       <c r="D689" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E689" s="5" t="inlineStr">
@@ -33074,7 +32634,7 @@
       </c>
       <c r="D693" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E693" s="5" t="inlineStr">
@@ -33114,7 +32674,7 @@
       </c>
       <c r="D694" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E694" s="5" t="inlineStr">
@@ -33274,7 +32834,7 @@
       </c>
       <c r="D698" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E698" s="5" t="inlineStr">
@@ -33314,7 +32874,7 @@
       </c>
       <c r="D699" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E699" s="5" t="inlineStr">
@@ -33474,7 +33034,7 @@
       </c>
       <c r="D703" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E703" s="5" t="inlineStr">
@@ -33514,7 +33074,7 @@
       </c>
       <c r="D704" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E704" s="5" t="inlineStr">
@@ -33674,7 +33234,7 @@
       </c>
       <c r="D708" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E708" s="5" t="inlineStr">
@@ -33714,7 +33274,7 @@
       </c>
       <c r="D709" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E709" s="5" t="inlineStr">
@@ -33874,7 +33434,7 @@
       </c>
       <c r="D713" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E713" s="5" t="inlineStr">
@@ -33914,7 +33474,7 @@
       </c>
       <c r="D714" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E714" s="5" t="inlineStr">
@@ -34074,7 +33634,7 @@
       </c>
       <c r="D718" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E718" s="5" t="inlineStr">
@@ -34114,7 +33674,7 @@
       </c>
       <c r="D719" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E719" s="5" t="inlineStr">
@@ -34274,7 +33834,7 @@
       </c>
       <c r="D723" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E723" s="5" t="inlineStr">
@@ -34314,7 +33874,7 @@
       </c>
       <c r="D724" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E724" s="5" t="inlineStr">
@@ -34474,7 +34034,7 @@
       </c>
       <c r="D728" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E728" s="5" t="inlineStr">
@@ -34514,7 +34074,7 @@
       </c>
       <c r="D729" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E729" s="5" t="inlineStr">
@@ -34674,7 +34234,7 @@
       </c>
       <c r="D733" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="E733" s="5" t="inlineStr">
@@ -34714,7 +34274,7 @@
       </c>
       <c r="D734" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="E734" s="5" t="inlineStr">
@@ -35074,7 +34634,7 @@
       </c>
       <c r="D743" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： APS(出荷基準)</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="E743" s="5" t="inlineStr">
@@ -35154,7 +34714,7 @@
       </c>
       <c r="D745" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 塗料系統(出荷基準)の複製</t>
+          <t>分類名（リファイン_屋根壁分割）</t>
         </is>
       </c>
       <c r="E745" s="5" t="inlineStr">
@@ -35234,7 +34794,7 @@
       </c>
       <c r="D747" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： カテゴリー(出荷基準)</t>
+          <t>商品カテゴリ(親カテゴリ)</t>
         </is>
       </c>
       <c r="E747" s="5" t="inlineStr">
@@ -35394,7 +34954,7 @@
       </c>
       <c r="D751" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 加盟グループ_プロテック（フィラーⅡ含）</t>
+          <t>加盟グループ_プロテック（フィラー2Ⅱ含）</t>
         </is>
       </c>
       <c r="E751" s="5" t="inlineStr">
@@ -35474,7 +35034,7 @@
       </c>
       <c r="D753" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of アステック加盟種別(出荷基準)の複製</t>
+          <t>アステック加盟種別</t>
         </is>
       </c>
       <c r="E753" s="5" t="inlineStr">
@@ -35634,7 +35194,7 @@
       </c>
       <c r="D757" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of カイゼンReペイントサービス</t>
+          <t>カイゼンReペイント（NULL・空削除）</t>
         </is>
       </c>
       <c r="E757" s="5" t="inlineStr">
@@ -35954,7 +35514,7 @@
       </c>
       <c r="D765" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： APS(出荷基準)</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="E765" s="5" t="inlineStr">
@@ -36034,7 +35594,7 @@
       </c>
       <c r="D767" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 塗料系統(出荷基準)の複製</t>
+          <t>分類名（リファイン_屋根壁分割）</t>
         </is>
       </c>
       <c r="E767" s="5" t="inlineStr">
@@ -36114,7 +35674,7 @@
       </c>
       <c r="D769" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： カテゴリー(出荷基準)</t>
+          <t>商品カテゴリ(親カテゴリ)</t>
         </is>
       </c>
       <c r="E769" s="5" t="inlineStr">
@@ -36274,7 +35834,7 @@
       </c>
       <c r="D773" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 加盟グループ_プロテック（フィラーⅡ含）</t>
+          <t>加盟グループ_プロテック（フィラー2Ⅱ含）</t>
         </is>
       </c>
       <c r="E773" s="5" t="inlineStr">
@@ -36354,7 +35914,7 @@
       </c>
       <c r="D775" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of アステック加盟種別(出荷基準)の複製</t>
+          <t>アステック加盟種別</t>
         </is>
       </c>
       <c r="E775" s="5" t="inlineStr">
@@ -36514,7 +36074,7 @@
       </c>
       <c r="D779" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of カイゼンReペイントサービス</t>
+          <t>カイゼンReペイント（NULL・空削除）</t>
         </is>
       </c>
       <c r="E779" s="5" t="inlineStr">
@@ -36834,7 +36394,7 @@
       </c>
       <c r="D787" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： APS(出荷基準)</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="E787" s="5" t="inlineStr">
@@ -36914,7 +36474,7 @@
       </c>
       <c r="D789" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 塗料系統(出荷基準)の複製</t>
+          <t>分類名（リファイン_屋根壁分割）</t>
         </is>
       </c>
       <c r="E789" s="5" t="inlineStr">
@@ -36994,7 +36554,7 @@
       </c>
       <c r="D791" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： カテゴリー(出荷基準)</t>
+          <t>商品カテゴリ(親カテゴリ)</t>
         </is>
       </c>
       <c r="E791" s="5" t="inlineStr">
@@ -37154,7 +36714,7 @@
       </c>
       <c r="D795" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 加盟グループ_プロテック（フィラーⅡ含）</t>
+          <t>加盟グループ_プロテック（フィラー2Ⅱ含）</t>
         </is>
       </c>
       <c r="E795" s="5" t="inlineStr">
@@ -37234,7 +36794,7 @@
       </c>
       <c r="D797" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of アステック加盟種別(出荷基準)の複製</t>
+          <t>アステック加盟種別</t>
         </is>
       </c>
       <c r="E797" s="5" t="inlineStr">
@@ -37247,14 +36807,14 @@
           <t>ER_現場名入り受注</t>
         </is>
       </c>
-      <c r="G797" s="14" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="G797" s="13" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="H797" s="5" t="inlineStr">
         <is>
-          <t>カラム無し</t>
+          <t>カラム有り</t>
         </is>
       </c>
     </row>
@@ -37394,7 +36954,7 @@
       </c>
       <c r="D801" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of カイゼンReペイントサービス</t>
+          <t>カイゼンReペイント（NULL・空削除）</t>
         </is>
       </c>
       <c r="E801" s="5" t="inlineStr">
@@ -37714,7 +37274,7 @@
       </c>
       <c r="D809" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： APS(出荷基準)</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="E809" s="5" t="inlineStr">
@@ -37794,7 +37354,7 @@
       </c>
       <c r="D811" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 塗料系統(出荷基準)の複製</t>
+          <t>分類名（リファイン_屋根壁分割）</t>
         </is>
       </c>
       <c r="E811" s="5" t="inlineStr">
@@ -37874,7 +37434,7 @@
       </c>
       <c r="D813" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 次の複製： カテゴリー(出荷基準)</t>
+          <t>商品カテゴリ(親カテゴリ)</t>
         </is>
       </c>
       <c r="E813" s="5" t="inlineStr">
@@ -38034,7 +37594,7 @@
       </c>
       <c r="D817" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of 加盟グループ_プロテック（フィラーⅡ含）</t>
+          <t>加盟グループ_プロテック（フィラー2Ⅱ含）</t>
         </is>
       </c>
       <c r="E817" s="5" t="inlineStr">
@@ -38114,7 +37674,7 @@
       </c>
       <c r="D819" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of アステック加盟種別(出荷基準)の複製</t>
+          <t>アステック加盟種別</t>
         </is>
       </c>
       <c r="E819" s="5" t="inlineStr">
@@ -38274,7 +37834,7 @@
       </c>
       <c r="D823" s="5" t="inlineStr">
         <is>
-          <t>Duplicate of カイゼンReペイントサービス</t>
+          <t>カイゼンReペイント（NULL・空削除）</t>
         </is>
       </c>
       <c r="E823" s="5" t="inlineStr">
@@ -38311,7 +37871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -38386,7 +37946,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -38408,7 +37968,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -38430,7 +37990,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -38447,7 +38007,7 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>■ 未応答カード一覧（12件）</t>
+          <t>■ 未応答カード一覧（10件）</t>
         </is>
       </c>
     </row>
@@ -38491,7 +38051,7 @@
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
@@ -38513,29 +38073,29 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均）</t>
+          <t>数値進捗（施工店）3ヶ月集計</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>コラボス_契約率移動平均用</t>
+          <t>コラボス＋リペイント（昨対集計用）</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
@@ -38552,12 +38112,12 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
@@ -38574,19 +38134,19 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>元請会社名</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>数値進捗（施工店）3ヶ月集計</t>
+          <t>数値進捗（施工店）</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -38596,12 +38156,12 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
@@ -38618,12 +38178,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
@@ -38640,34 +38200,34 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>元請会社名</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>数値進捗（施工店）</t>
+          <t>契約率（3ヶ月移動平均）</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>コラボス＋リペイント（昨対集計用）</t>
+          <t>コラボス_契約率移動平均用</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
@@ -38684,56 +38244,12 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>契約率（3ヶ月移動平均）</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>コラボス_契約率移動平均用</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>契約率（3ヶ月移動平均）</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>コラボス_契約率移動平均用</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
@@ -39316,7 +38832,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金なし）</t>
+          <t>コーナン（加盟金なし）名</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -39382,7 +38898,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>コーナン（加盟金あり）</t>
+          <t>コーナン（加盟金あり）名</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -39443,7 +38959,7 @@
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>コーナン（加盟金なし）</t>
+          <t>コーナン（加盟金なし）名</t>
         </is>
       </c>
     </row>
@@ -39509,7 +39025,7 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>コーナン（加盟金あり）</t>
+          <t>コーナン（加盟金あり）名</t>
         </is>
       </c>
     </row>
@@ -39530,7 +39046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -39583,7 +39099,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -39605,7 +39121,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -39627,7 +39143,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -39644,7 +39160,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>■ 未応答カード一覧（14件）</t>
+          <t>■ 未応答カード一覧（7件）</t>
         </is>
       </c>
     </row>
@@ -39688,14 +39204,14 @@
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>前期 完工粗利進捗（完工・未完工集計）</t>
+          <t>坂本あテスト＿  完工粗利進捗（完工・未完工集計）</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
@@ -39705,19 +39221,19 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>坂本あテスト＿  完工粗利進捗（完工・未完工集計）</t>
+          <t>月別実績集計表（昨対比較含む）</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -39732,14 +39248,14 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>坂本あテスト＿  完工粗利進捗（完工・未完工集計）</t>
+          <t>前期 数字進捗集計（案件・見積・契約）</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
@@ -39749,19 +39265,19 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>月別実績集計表（昨対比較含む）</t>
+          <t>完工粗利進捗（完工・未完工集計）</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -39776,14 +39292,14 @@
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>月別実績集計表（昨対比較含む）</t>
+          <t>前期 月別実績集計表（昨対比較含む)</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -39793,19 +39309,19 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット（コラボス）</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>前期 数字進捗集計（案件・見積・契約）</t>
+          <t>数字進捗集計（案件・見積・契約）</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -39820,161 +39336,7 @@
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>前期 数字進捗集計（案件・見積・契約）</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント（日別集計）</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>完工粗利進捗（完工・未完工集計）</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント（日別集計）</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>ユニット（コラボス）</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>ユニット（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>完工粗利進捗（完工・未完工集計）</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント（日別集計）</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>前期 月別実績集計表（昨対比較含む)</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント（日別集計）</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>ユニット（コラボス）</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>ユニット（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>前期 月別実績集計表（昨対比較含む)</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント（日別集計）</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>数字進捗集計（案件・見積・契約）</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント（日別集計）</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>ユニット（コラボス）</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>ユニット（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>数字進捗集計（案件・見積・契約）</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>コラボス＋リペイント（日別集計）</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
     </row>
@@ -39995,7 +39357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -40048,7 +39410,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -40070,7 +39432,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>元請会社</t>
+          <t>元請会社(表示修正)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -40092,7 +39454,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>営業担当</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -40109,7 +39471,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>■ 未応答カード一覧（1件）</t>
+          <t>■ 未応答カード一覧（3件）</t>
         </is>
       </c>
     </row>
@@ -40153,7 +39515,51 @@
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>ユニット（コラボス）</t>
+          <t>ユニット</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>コラボス_元請会社別新規案件数（昨対比）.</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>コラボス＋リペイント（昨対集計用）</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>元請会社名（コラボス）</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>元請会社(表示修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>コラボス_元請会社別新規案件数（昨対比）.</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>コラボス＋リペイント（昨対集計用）</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>営業担当（コラボス）</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
@@ -40174,7 +39580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -40227,7 +39633,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -40249,7 +39655,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -40293,7 +39699,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>元請会社（DCMまとめ）</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -40332,7 +39738,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>■ 未応答カード一覧（12件）</t>
+          <t>■ 未応答カード一覧（8件）</t>
         </is>
       </c>
     </row>
@@ -40376,7 +39782,7 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
@@ -40398,14 +39804,14 @@
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>契約率（3ヶ月移動平均/60万円以上）</t>
+          <t>契約率（12ヶ月移動平均）</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -40415,12 +39821,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
@@ -40437,19 +39843,19 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均）</t>
+          <t>契約率（3ヶ月移動平均）</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -40459,19 +39865,19 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>営業担当（コラボス）</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>契約率（12ヶ月移動平均）</t>
+          <t>契約率（3ヶ月移動平均）</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -40481,19 +39887,19 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>コラボス集計</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>元請会社名</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>契約率（3ヶ月移動平均）</t>
+          <t>契約率（12ヶ月移動平均/60万円以上）</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -40508,14 +39914,14 @@
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>営業担当（コラボス）</t>
+          <t>営業担当（文字化け修正）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>契約率（3ヶ月移動平均）</t>
+          <t>契約率（12ヶ月移動平均/60万円以上）</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
@@ -40530,95 +39936,7 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>契約率（3ヶ月移動平均）</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>コラボス_契約率移動平均用</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>契約率（12ヶ月移動平均/60万円以上）</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>コラボス_契約率移動平均用</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>営業担当（コラボス）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>契約率（12ヶ月移動平均/60万円以上）</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>コラボス_契約率移動平均用</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>コラボス集計</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>契約率（12ヶ月移動平均/60万円以上）</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>コラボス_契約率移動平均用</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>元請会社名</t>
+          <t>スポットチェンジ判断</t>
         </is>
       </c>
     </row>
